--- a/docs/ENVIO MAPA.xlsx
+++ b/docs/ENVIO MAPA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuri.toso\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.veloso\Documents\Desenvolvimento - Interno\mapa-de-estoque\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4939E410-5E7B-4576-B837-AC96F28FC55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5422DE41-C7E6-4617-A5F4-389B67593F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="107">
   <si>
     <t>ID FABRICANTE</t>
   </si>
@@ -115,9 +115,6 @@
     <t>HERBAMED LABORATORIO NUTRACEUTICO LTDA</t>
   </si>
   <si>
-    <t>kirian.cunha@herbamned.com.br</t>
-  </si>
-  <si>
     <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
   </si>
   <si>
@@ -188,13 +185,169 @@
   </si>
   <si>
     <t>antonio.Barbara@viatris.com</t>
+  </si>
+  <si>
+    <t>CREMER S.A.</t>
+  </si>
+  <si>
+    <t>MIKELY TAMY</t>
+  </si>
+  <si>
+    <t>mateus.lourinho@cremer.com.br</t>
+  </si>
+  <si>
+    <t>B S DISTRIBUIDORA DE PRODUTOS DE HIGIENE LTDA</t>
+  </si>
+  <si>
+    <t>mateus.marques@baruel.com.br</t>
+  </si>
+  <si>
+    <t>OMRON HEALTHCARE BRASIL INDUSTRIA E COMERCIO DE PRODUTOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>anacosta.rep@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEBON FARMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOICI </t>
+  </si>
+  <si>
+    <t>jprata42@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTISAUDE </t>
+  </si>
+  <si>
+    <t>gcmg@wplab.ind.br</t>
+  </si>
+  <si>
+    <t>CIFARMA CIENTIFICA FARMACEUTICA</t>
+  </si>
+  <si>
+    <t>gleyson@cifarma.com.br</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUROFARMA OTC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">andrea.vasconcellos@eurofarma.com </t>
+  </si>
+  <si>
+    <t>BAYER OTC</t>
+  </si>
+  <si>
+    <t>chafic.publo@terra.com.br</t>
+  </si>
+  <si>
+    <t>ABBOTT LABORATÓRIOS DO BRASIL</t>
+  </si>
+  <si>
+    <t>mauricio.ramos@abbott.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTALIA PRODUTOS QUÍMICOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">herbert.domingues@cristalia.com.br </t>
+  </si>
+  <si>
+    <t>MERCK RX</t>
+  </si>
+  <si>
+    <t>davi.bertolini@merckgroup.com</t>
+  </si>
+  <si>
+    <t>kirian.cunha@herbamed.com.br</t>
+  </si>
+  <si>
+    <t>19847 - 7149</t>
+  </si>
+  <si>
+    <t>BLAU FARMACEUTICA S.A.(BLAU)</t>
+  </si>
+  <si>
+    <t>GELIANA</t>
+  </si>
+  <si>
+    <t>jana.romano@blau.com</t>
+  </si>
+  <si>
+    <t>LABORATÓRIO QUÍMICO FARMACEUTICO BERGAMO</t>
+  </si>
+  <si>
+    <t>45213-45078-45483</t>
+  </si>
+  <si>
+    <t>EUROFARMA (GENERICOS) LABORATORIOS S.A</t>
+  </si>
+  <si>
+    <t>Hugo.Queiroz@eurofarma.com</t>
+  </si>
+  <si>
+    <t>FLORA NECTAR INDUSTRIA COMERCIO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>edivaldorodrigues1972@gmail.com</t>
+  </si>
+  <si>
+    <t>50640-118363-50655</t>
+  </si>
+  <si>
+    <t>GERMED GENERICOS</t>
+  </si>
+  <si>
+    <t>marina.vidal@gruponc.net.br</t>
+  </si>
+  <si>
+    <t>LABORATORIO CATARINENSE S. A.</t>
+  </si>
+  <si>
+    <t>MEDIFLORA PRODUTOS NATURAIS E APICOLAS LTDA</t>
+  </si>
+  <si>
+    <t>naturezadaserrapetr@gmail.com</t>
+  </si>
+  <si>
+    <t>MERCK GENERICOS</t>
+  </si>
+  <si>
+    <t>112481-112489</t>
+  </si>
+  <si>
+    <t>MEDLEY (GENÉRICOS) FARMACEUTICA LTDA</t>
+  </si>
+  <si>
+    <t>Alexandre.Lopes@medley.com.br</t>
+  </si>
+  <si>
+    <t>50753-50754-50755-50756</t>
+  </si>
+  <si>
+    <t>NOVA QUIMICA</t>
+  </si>
+  <si>
+    <t>renan.santos@novaquimicagenericos.com.br</t>
+  </si>
+  <si>
+    <t>LEGRAND GENERICO</t>
+  </si>
+  <si>
+    <t>Ygor.barge@legrandpharma.com.br</t>
+  </si>
+  <si>
+    <t>51079-104752-104753-104754</t>
+  </si>
+  <si>
+    <t>marilene.eduardo@catarinensepharma.com.br</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -213,13 +366,57 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -246,10 +443,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -263,11 +461,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -570,11 +814,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -589,7 +833,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -662,7 +906,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -686,7 +930,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -718,7 +962,7 @@
         <v>122992</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
@@ -734,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -742,7 +986,7 @@
         <v>123174</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
@@ -758,7 +1002,7 @@
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -886,7 +1130,7 @@
         <v>13963</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>12</v>
@@ -951,8 +1195,8 @@
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>31</v>
+      <c r="J15" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -960,7 +1204,7 @@
         <v>30314</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>12</v>
@@ -976,7 +1220,7 @@
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -984,7 +1228,7 @@
         <v>39010</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>12</v>
@@ -1008,7 +1252,7 @@
         <v>44425</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>12</v>
@@ -1032,7 +1276,7 @@
         <v>7127</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>12</v>
@@ -1050,7 +1294,7 @@
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1058,7 +1302,7 @@
         <v>47658</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>12</v>
@@ -1074,7 +1318,7 @@
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1082,7 +1326,7 @@
         <v>104634</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>12</v>
@@ -1098,7 +1342,7 @@
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -1106,7 +1350,7 @@
         <v>52878</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>12</v>
@@ -1122,7 +1366,7 @@
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -1130,7 +1374,7 @@
         <v>58650</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>12</v>
@@ -1146,15 +1390,15 @@
         <v>13</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>12</v>
@@ -1170,7 +1414,7 @@
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -1178,7 +1422,7 @@
         <v>46292</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>12</v>
@@ -1194,14 +1438,551 @@
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>7485</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>55</v>
       </c>
+      <c r="C26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>23975</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>43176</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>47476</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>107151</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>49913</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>45484</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>22866</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>21729</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>27878</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>35729</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>7181</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>19117</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>20285</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <v>22287</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>27499</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J6" r:id="rId1" xr:uid="{9791F816-AA06-4D59-AED6-32837D568F3D}"/>
     <hyperlink ref="J7" r:id="rId2" xr:uid="{232E5092-F983-4133-A14B-FEF596F279D2}"/>
     <hyperlink ref="J25" r:id="rId3" xr:uid="{5249B9AE-EB38-4E91-BFD1-3D2B5D840CC0}"/>
+    <hyperlink ref="J26" r:id="rId4" xr:uid="{102A299D-9405-467D-A338-99BE13828AE8}"/>
+    <hyperlink ref="J27" r:id="rId5" xr:uid="{0CA6C4B7-6F96-42FC-8784-88994DB3A77D}"/>
+    <hyperlink ref="J28" r:id="rId6" xr:uid="{9AA2C8E6-8A1C-4371-859B-ACD40B39CFC6}"/>
+    <hyperlink ref="J30" r:id="rId7" xr:uid="{5ACA3C95-40B7-46A6-8537-5D1484E9D1C0}"/>
+    <hyperlink ref="J15" r:id="rId8" xr:uid="{6F0B471E-DB43-4334-AC70-44E5463FD9DD}"/>
+    <hyperlink ref="J29" r:id="rId9" xr:uid="{89386F5F-DC0B-4223-B9AA-DCB36A628539}"/>
+    <hyperlink ref="J37" r:id="rId10" xr:uid="{D61F6EC0-90F6-440D-89EA-18716E977648}"/>
+    <hyperlink ref="J38" r:id="rId11" xr:uid="{A2B9810A-E68E-45AD-9268-07BC0A06E8F7}"/>
+    <hyperlink ref="J42" r:id="rId12" xr:uid="{F8B32B5D-3A34-4EFD-B3A0-B496AD2F74EB}"/>
+    <hyperlink ref="J43" r:id="rId13" xr:uid="{F14AD8A1-C901-43CB-8A87-667222469056}"/>
+    <hyperlink ref="J45" r:id="rId14" xr:uid="{5985511B-5A12-447A-B36C-8FA973F88D90}"/>
+    <hyperlink ref="J47" r:id="rId15" xr:uid="{285DDA20-E050-4D54-91A6-6F4C937F2634}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
